--- a/artfynd/A 45007-2023 artfynd.xlsx
+++ b/artfynd/A 45007-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122619393</v>
+        <v>122619108</v>
       </c>
       <c r="B2" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602667</v>
+        <v>602652</v>
       </c>
       <c r="R2" t="n">
-        <v>6988250</v>
+        <v>6988282</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122619374</v>
+        <v>122619393</v>
       </c>
       <c r="B3" t="n">
         <v>57383</v>
@@ -842,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602666</v>
+        <v>602667</v>
       </c>
       <c r="R3" t="n">
-        <v>6988269</v>
+        <v>6988250</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -907,22 +902,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122619108</v>
+        <v>122619374</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,16 +930,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -964,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602652</v>
+        <v>602666</v>
       </c>
       <c r="R4" t="n">
-        <v>6988282</v>
+        <v>6988269</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1004,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,12 +1024,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 45007-2023 artfynd.xlsx
+++ b/artfynd/A 45007-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122619108</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>122619393</v>
       </c>
       <c r="B3" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>122619374</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 45007-2023 artfynd.xlsx
+++ b/artfynd/A 45007-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122619108</v>
+        <v>122619393</v>
       </c>
       <c r="B2" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602652</v>
+        <v>602667</v>
       </c>
       <c r="R2" t="n">
-        <v>6988282</v>
+        <v>6988250</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122619393</v>
+        <v>122619374</v>
       </c>
       <c r="B3" t="n">
         <v>57384</v>
@@ -837,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602667</v>
+        <v>602666</v>
       </c>
       <c r="R3" t="n">
-        <v>6988250</v>
+        <v>6988269</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -902,22 +907,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122619374</v>
+        <v>122619108</v>
       </c>
       <c r="B4" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,16 +935,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -959,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602666</v>
+        <v>602652</v>
       </c>
       <c r="R4" t="n">
-        <v>6988269</v>
+        <v>6988282</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,12 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,12 +1024,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 45007-2023 artfynd.xlsx
+++ b/artfynd/A 45007-2023 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122619374</v>
+        <v>122619108</v>
       </c>
       <c r="B3" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,16 +813,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602666</v>
+        <v>602652</v>
       </c>
       <c r="R3" t="n">
-        <v>6988269</v>
+        <v>6988282</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,22 +902,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122619108</v>
+        <v>122619374</v>
       </c>
       <c r="B4" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,16 +930,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -964,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602652</v>
+        <v>602666</v>
       </c>
       <c r="R4" t="n">
-        <v>6988282</v>
+        <v>6988269</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1004,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,12 +1024,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 45007-2023 artfynd.xlsx
+++ b/artfynd/A 45007-2023 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122619108</v>
+        <v>122619393</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,16 +813,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602652</v>
+        <v>602667</v>
       </c>
       <c r="R3" t="n">
-        <v>6988282</v>
+        <v>6988250</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122619393</v>
+        <v>122619108</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,16 +935,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -959,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602667</v>
+        <v>602652</v>
       </c>
       <c r="R4" t="n">
-        <v>6988250</v>
+        <v>6988282</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,12 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 45007-2023 artfynd.xlsx
+++ b/artfynd/A 45007-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122619374</v>
+        <v>122619393</v>
       </c>
       <c r="B2" t="n">
         <v>57478</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602666</v>
+        <v>602667</v>
       </c>
       <c r="R2" t="n">
-        <v>6988269</v>
+        <v>6988250</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,19 +785,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122619393</v>
+        <v>122619374</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602667</v>
+        <v>602666</v>
       </c>
       <c r="R3" t="n">
-        <v>6988250</v>
+        <v>6988269</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -907,12 +907,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 45007-2023 artfynd.xlsx
+++ b/artfynd/A 45007-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1034,6 +1034,108 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122941826</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90944</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kajsamyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>602562</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6988194</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45007-2023 artfynd.xlsx
+++ b/artfynd/A 45007-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122619393</v>
+        <v>122619374</v>
       </c>
       <c r="B2" t="n">
         <v>57478</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602667</v>
+        <v>602666</v>
       </c>
       <c r="R2" t="n">
-        <v>6988250</v>
+        <v>6988269</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122619374</v>
+        <v>122619108</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,16 +813,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602666</v>
+        <v>602652</v>
       </c>
       <c r="R3" t="n">
-        <v>6988269</v>
+        <v>6988282</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,22 +902,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122619108</v>
+        <v>122619393</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,16 +930,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -964,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602652</v>
+        <v>602667</v>
       </c>
       <c r="R4" t="n">
-        <v>6988282</v>
+        <v>6988250</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1004,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 45007-2023 artfynd.xlsx
+++ b/artfynd/A 45007-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122619374</v>
+        <v>122619393</v>
       </c>
       <c r="B2" t="n">
         <v>57478</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602666</v>
+        <v>602667</v>
       </c>
       <c r="R2" t="n">
-        <v>6988269</v>
+        <v>6988250</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,12 +785,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -914,7 +914,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122619393</v>
+        <v>122619374</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602667</v>
+        <v>602666</v>
       </c>
       <c r="R4" t="n">
-        <v>6988250</v>
+        <v>6988269</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,12 +1024,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1039,7 +1039,7 @@
         <v>122941826</v>
       </c>
       <c r="B5" t="n">
-        <v>90944</v>
+        <v>90952</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 45007-2023 artfynd.xlsx
+++ b/artfynd/A 45007-2023 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>122941826</v>
       </c>
       <c r="B5" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 45007-2023 artfynd.xlsx
+++ b/artfynd/A 45007-2023 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>122941826</v>
       </c>
       <c r="B5" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 45007-2023 artfynd.xlsx
+++ b/artfynd/A 45007-2023 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>122941826</v>
       </c>
       <c r="B5" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 45007-2023 artfynd.xlsx
+++ b/artfynd/A 45007-2023 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>122941826</v>
       </c>
       <c r="B5" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 45007-2023 artfynd.xlsx
+++ b/artfynd/A 45007-2023 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>122941826</v>
       </c>
       <c r="B5" t="n">
-        <v>90983</v>
+        <v>91166</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,6 +1070,9 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kajsamyran, Ång</t>
@@ -1106,12 +1109,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-02-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-02-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,6 +1123,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 45007-2023 artfynd.xlsx
+++ b/artfynd/A 45007-2023 artfynd.xlsx
@@ -1039,12 +1039,7 @@
         <v>122941826</v>
       </c>
       <c r="B5" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 45007-2023 artfynd.xlsx
+++ b/artfynd/A 45007-2023 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>122941826</v>
       </c>
       <c r="B5" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 45007-2023 artfynd.xlsx
+++ b/artfynd/A 45007-2023 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>122941826</v>
       </c>
       <c r="B5" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 45007-2023 artfynd.xlsx
+++ b/artfynd/A 45007-2023 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>122941826</v>
       </c>
       <c r="B5" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 45007-2023 artfynd.xlsx
+++ b/artfynd/A 45007-2023 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>122941826</v>
       </c>
       <c r="B5" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 45007-2023 artfynd.xlsx
+++ b/artfynd/A 45007-2023 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>122941826</v>
       </c>
       <c r="B5" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 45007-2023 artfynd.xlsx
+++ b/artfynd/A 45007-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122619393</v>
+        <v>122941826</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kajsamyran, Kajsamyran, Ång</t>
+          <t>Kajsamyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602667</v>
+        <v>602562</v>
       </c>
       <c r="R2" t="n">
-        <v>6988250</v>
+        <v>6988194</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,59 +746,40 @@
           <t>2025-02-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-15</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122619108</v>
+        <v>133422108</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,42 +787,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kajsamyran, Kajsamyran, Ång</t>
+          <t>Malmån, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602652</v>
+        <v>602572</v>
       </c>
       <c r="R3" t="n">
-        <v>6988282</v>
+        <v>6988198</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,22 +848,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-02-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:31</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-02-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:31</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,70 +868,67 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Teo Jernkvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Teo Jernkvist, Ulrika Westling</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122619374</v>
+        <v>133422111</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kajsamyran, Kajsamyran, Ång</t>
+          <t>Malmån, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602666</v>
+        <v>602548</v>
       </c>
       <c r="R4" t="n">
-        <v>6988269</v>
+        <v>6988198</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,27 +952,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-02-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:55</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-02-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,63 +972,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Teo Jernkvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Teo Jernkvist, Ulrika Westling</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122941826</v>
+        <v>122619108</v>
       </c>
       <c r="B5" t="n">
-        <v>91236</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kajsamyran, Ång</t>
+          <t>Kajsamyran, Kajsamyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>602562</v>
+        <v>602652</v>
       </c>
       <c r="R5" t="n">
-        <v>6988194</v>
+        <v>6988282</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,40 +1057,49 @@
           <t>2025-02-15</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-15</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133422108</v>
+        <v>122618779</v>
       </c>
       <c r="B6" t="n">
-        <v>91959</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,44 +1107,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Malmån, Ång</t>
+          <t>Kajsamyran, Kajsamyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602572</v>
+        <v>602522</v>
       </c>
       <c r="R6" t="n">
-        <v>6988198</v>
+        <v>6988200</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,12 +1166,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-02-15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-02-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,39 +1201,39 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Teo Jernkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Teo Jernkvist, Ulrika Westling</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133422110</v>
+        <v>122618800</v>
       </c>
       <c r="B7" t="n">
-        <v>58079</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1269,28 +1241,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Malmån, Ång</t>
+          <t>Kajsamyran, Kajsamyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>602571</v>
+        <v>602516</v>
       </c>
       <c r="R7" t="n">
-        <v>6988198</v>
+        <v>6988193</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,12 +1283,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-02-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-02-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,22 +1318,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Teo Jernkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Teo Jernkvist, Ulrika Westling</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133422111</v>
+        <v>122619374</v>
       </c>
       <c r="B8" t="n">
-        <v>79359</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,44 +1341,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Malmån, Ång</t>
+          <t>Kajsamyran, Kajsamyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>602548</v>
+        <v>602666</v>
       </c>
       <c r="R8" t="n">
-        <v>6988198</v>
+        <v>6988269</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1418,12 +1400,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-02-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-02-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1438,15 +1435,575 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122619393</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kajsamyran, Kajsamyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>602667</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6988250</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122858108</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kajsamyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>602731</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6988240</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133412644</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kajsamyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>602552</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6988328</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska spår ifrån i år.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133412666</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kajsamyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>602526</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6988201</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133422110</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58079</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Malmån, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>602571</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6988198</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Teo Jernkvist</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Teo Jernkvist, Ulrika Westling</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45007-2023 artfynd.xlsx
+++ b/artfynd/A 45007-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122941826</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -877,6 +887,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133422108</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133422111</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1093,6 +1113,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122619108</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122618779</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1327,6 +1357,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122618800</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1444,6 +1479,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122619374</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1561,6 +1601,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122619393</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1684,6 +1729,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122858108</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1794,6 +1844,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133412644</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1899,6 +1954,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133412666</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2004,8 +2064,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133422110</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>